--- a/Excel/EquipSetConfig.xlsx
+++ b/Excel/EquipSetConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -1027,7 +1032,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:J17"/>
+  <dimension ref="C1:J30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1386,6 +1391,282 @@
       </c>
       <c r="I17" s="1">
         <v>2</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:9">
+      <c r="C19" s="1">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3</v>
+      </c>
+      <c r="G19" s="1">
+        <v>10004</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:9">
+      <c r="C20" s="1">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>6</v>
+      </c>
+      <c r="G20" s="1">
+        <v>10001</v>
+      </c>
+      <c r="H20" s="1">
+        <v>4</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:9">
+      <c r="C21" s="1">
+        <v>15</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1">
+        <v>8</v>
+      </c>
+      <c r="G21" s="1">
+        <v>10002</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:9">
+      <c r="C22" s="1">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="1">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1">
+        <v>10003</v>
+      </c>
+      <c r="H22" s="1">
+        <v>2</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:9">
+      <c r="C23" s="1">
+        <v>17</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1">
+        <v>10005</v>
+      </c>
+      <c r="H23" s="1">
+        <v>2</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:9">
+      <c r="C24" s="1">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2</v>
+      </c>
+      <c r="F24" s="1">
+        <v>6</v>
+      </c>
+      <c r="G24" s="1">
+        <v>10001</v>
+      </c>
+      <c r="H24" s="1">
+        <v>4</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:9">
+      <c r="C25" s="1">
+        <v>19</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+      <c r="F25" s="1">
+        <v>8</v>
+      </c>
+      <c r="G25" s="1">
+        <v>10002</v>
+      </c>
+      <c r="H25" s="1">
+        <v>2</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:9">
+      <c r="C26" s="1">
+        <v>20</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="F26" s="1">
+        <v>10</v>
+      </c>
+      <c r="G26" s="1">
+        <v>10003</v>
+      </c>
+      <c r="H26" s="1">
+        <v>2</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:9">
+      <c r="C27" s="1">
+        <v>21</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1">
+        <v>3</v>
+      </c>
+      <c r="G27" s="1">
+        <v>10006</v>
+      </c>
+      <c r="H27" s="1">
+        <v>2</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:9">
+      <c r="C28" s="1">
+        <v>22</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2</v>
+      </c>
+      <c r="F28" s="1">
+        <v>6</v>
+      </c>
+      <c r="G28" s="1">
+        <v>10001</v>
+      </c>
+      <c r="H28" s="1">
+        <v>4</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:9">
+      <c r="C29" s="1">
+        <v>23</v>
+      </c>
+      <c r="D29" s="1">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2</v>
+      </c>
+      <c r="F29" s="1">
+        <v>8</v>
+      </c>
+      <c r="G29" s="1">
+        <v>10002</v>
+      </c>
+      <c r="H29" s="1">
+        <v>2</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:9">
+      <c r="C30" s="1">
+        <v>24</v>
+      </c>
+      <c r="D30" s="1">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2</v>
+      </c>
+      <c r="F30" s="1">
+        <v>10</v>
+      </c>
+      <c r="G30" s="1">
+        <v>10003</v>
+      </c>
+      <c r="H30" s="1">
+        <v>2</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
